--- a/Tecnical test/Test_Case_HRSV_Dashboard.xlsx
+++ b/Tecnical test/Test_Case_HRSV_Dashboard.xlsx
@@ -512,6 +512,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -580,7 +581,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>17 Skenario (3 Login + 14 Form Karyawan Baru)</t>
+          <t>15 Skenario (3 Login + 12 Form Karyawan Baru)</t>
         </is>
       </c>
     </row>
@@ -592,7 +593,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>17 PASSED / 0 FAILED (Tingkat Keberhasilan: 100%)</t>
+          <t>15 PASSED / 0 FAILED (Tingkat Keberhasilan: 100%)</t>
         </is>
       </c>
     </row>
@@ -841,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -856,74 +857,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Modul</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Tipe</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Skenario Pengujian</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Langkah Pengujian</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Data Uji / Input (Lengkap 11 Field)</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Hasil yang Diharapkan (Expected)</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Hasil Aktual (Actual)</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2" ht="145" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC_KB_01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Tambah karyawan baru dengan data lengkap &amp; valid</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -932,7 +933,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Budi Santoso
 • Tempat Lahir: Jakarta
@@ -947,44 +948,44 @@
 • Upload Foto Selfie: selfie1.jpg</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Muncul notifikasi sukses: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Popup SweetAlert muncul: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="3" ht="145" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC_KB_02</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Tambah karyawan baru dengan centang checkbox alamat sama dengan KTP</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -993,7 +994,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Siti Aminah
 • Tempat Lahir: Bandung
@@ -1008,44 +1009,44 @@
 • Upload Foto Selfie: selfie2.jpg</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Muncul notifikasi sukses: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Popup SweetAlert muncul: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="4" ht="145" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC_KB_03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Tambah karyawan baru domisili berbeda dengan KTP</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1054,7 +1055,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Andi Wijaya
 • Tempat Lahir: Surabaya
@@ -1069,44 +1070,44 @@
 • Upload Foto Selfie: selfie3.jpg</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Muncul notifikasi sukses: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Popup SweetAlert muncul: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="145" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TC_KB_04</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Tambah karyawan baru wanita data lengkap</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1115,7 +1116,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Rina Kartika
 • Tempat Lahir: Medan
@@ -1130,44 +1131,44 @@
 • Upload Foto Selfie: selfie4.jpg</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Muncul notifikasi sukses: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Popup SweetAlert muncul: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="6" ht="145" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>TC_KB_05</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Validasi field Nama Lengkap kosong</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1176,7 +1177,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>• Nama Lengkap: (kosong)
 • Tempat Lahir: Jakarta
@@ -1191,44 +1192,44 @@
 • Upload Foto Selfie: selfie5.jpg</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Nama Lengkap tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Nama Lengkap tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7" ht="145" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>TC_KB_06</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Validasi field Nomor KTP kosong</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1237,7 +1238,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test KTP Kosong
 • Tempat Lahir: Jakarta
@@ -1252,44 +1253,44 @@
 • Upload Foto Selfie: selfie6.jpg</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Nomor KTP tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Nomor KTP tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="145" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>TC_KB_07</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Validasi Nomor KTP kurang dari 16 digit</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1298,7 +1299,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test KTP Pendek
 • Tempat Lahir: Jakarta
@@ -1313,44 +1314,44 @@
 • Upload Foto Selfie: selfie7.jpg</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Nomor KTP harus memiliki 16 digit!</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Nomor KTP harus memiliki 16 digit!</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="145" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>TC_KB_08</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Validasi field Email kosong</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1359,7 +1360,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test Email Kosong
 • Tempat Lahir: Jakarta
@@ -1374,44 +1375,44 @@
 • Upload Foto Selfie: selfie8.jpg</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Email tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Email tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="10" ht="145" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>TC_KB_09</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Validasi format Email tidak valid</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1420,7 +1421,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test Email Salah
 • Tempat Lahir: Jakarta
@@ -1435,44 +1436,44 @@
 • Upload Foto Selfie: selfie9.jpg</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Format alamat email salah!</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Format alamat email salah!</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="11" ht="145" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>TC_KB_10</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Validasi field Tanggal Lahir kosong</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1481,7 +1482,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test Tgl Lahir Kosong
 • Tempat Lahir: Jakarta
@@ -1496,44 +1497,44 @@
 • Upload Foto Selfie: selfie10.jpg</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: Tanggal Lahir tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: Tanggal Lahir tidak boleh kosong!</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="145" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TC_KB_11</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Validasi upload file KTP bukan gambar (.txt)</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1542,7 +1543,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test File Non-Gambar
 • Tempat Lahir: Jakarta
@@ -1557,44 +1558,44 @@
 • Upload Foto Selfie: selfie11.jpg</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Pesan validasi muncul: error read ktp image file: EOF</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Pesan validasi error muncul: error read ktp image file: EOF</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="13" ht="145" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>TC_KB_12</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Karyawan Baru</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Tambah karyawan baru centang checkbox domisili (Data 12)</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1. Login sebagai karyawan (TestAccountKaryawan1)
 2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
@@ -1603,7 +1604,7 @@
 5. Verifikasi notifikasi hasil submit</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>• Nama Lengkap: Test Checkbox
 • Tempat Lahir: Jakarta
@@ -1618,144 +1619,24 @@
 • Upload Foto Selfie: selfie12.jpg</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Muncul notifikasi sukses: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Popup SweetAlert muncul: Data karyawan baru berhasil dibuat</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="145" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>TC_KB_13</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Karyawan Baru</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Validasi Nomor HP non-angka (Karakter Huruf)</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>1. Login sebagai karyawan (TestAccountKaryawan1)
-2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
-3. Isi seluruh input form sesuai data uji &amp; upload file
-4. Klik tombol Submit (button-gradient-blue)
-5. Verifikasi notifikasi hasil submit</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>• Nama Lengkap: Test HP Non-Angka
-• Tempat Lahir: Jakarta
-• Tanggal Lahir: 1995-05-10
-• Nomor KTP: 3201010101010013
-• Nomor HP: abc123
-• Email: a13@sv.id
-• Tanggal Join: 2026-08-15
-• Alamat KTP: Jl. H No.8
-• Alamat Domisili: Jl. H No.8
-• Upload Foto KTP: ktp12.jpg
-• Upload Foto Selfie: selfie12.jpg</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Sistem menolak submit / muncul validasi: Format nomor HP tidak valid</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Data tidak sukses dibuat (Finding: Format nomor HP tidak valid tidak divalidasi backend)</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="145" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>TC_KB_14</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Karyawan Baru</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Validasi Tanggal Lahir di masa depan</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>1. Login sebagai karyawan (TestAccountKaryawan1)
-2. Buka Form Karyawan Baru (/#/form-karyawan-baru)
-3. Isi seluruh input form sesuai data uji &amp; upload file
-4. Klik tombol Submit (button-gradient-blue)
-5. Verifikasi notifikasi hasil submit</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>• Nama Lengkap: Test Tgl Lahir Depan
-• Tempat Lahir: Jakarta
-• Tanggal Lahir: 2030-01-01
-• Nomor KTP: 3201010101010014
-• Nomor HP: 081234567814
-• Email: a14@sv.id
-• Tanggal Join: 2026-08-15
-• Alamat KTP: Jl. I No.9
-• Alamat Domisili: Jl. I No.9
-• Upload Foto KTP: ktp1.jpg
-• Upload Foto Selfie: selfie1.jpg</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Sistem menolak submit / muncul validasi: Tanggal lahir tidak boleh di masa depan</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>Data tidak sukses dibuat (Finding: Tanggal lahir tidak boleh di masa depan tidak divalidasi backend)</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
+    <row r="14" ht="145" customHeight="1"/>
+    <row r="15" ht="145" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
